--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1129,15 +1129,15 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1560,15 +1560,15 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,15 +1991,15 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,15 +2422,15 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,98 +3574,98 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,74 +3910,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,27 +4116,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4146,15 +4146,15 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18118.77</t>
+          <t>9688.689</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,22 +4351,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>93.07</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.20</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>705.4</t>
+          <t>741.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>612.35</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>606.42</t>
+          <t>609.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>617.41</t>
+          <t>620.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>172.56</t>
+          <t>124.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.79</t>
+          <t>-76.47</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,27 +4547,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14250124193.0</t>
+          <t>7405253613.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8968390282.0</t>
+          <t>10011650749.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5294074253.1</t>
+          <t>5870589709.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2221550552.1</t>
+          <t>2337679186.88</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4577,15 +4577,15 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>663212878.2008342</t>
+          <t>817687226.2755579</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>1907718783.21</v>
+        <v>1667296140.69</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16158.888</t>
+          <t>18118.77</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4832,32 +4832,32 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,98 +4867,98 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>64.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.69</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>674.6</t>
+          <t>705.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>601.9</t>
+          <t>612.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>603.2</t>
+          <t>606.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>614.95</t>
+          <t>617.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>270.23</t>
+          <t>172.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-90.78</t>
+          <t>-83.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12410986088.0</t>
+          <t>14250124193.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6888940927.0</t>
+          <t>8968390282.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4033826236.5</t>
+          <t>5294074253.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1975526023.72</t>
+          <t>2221550552.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>436939077.2900687</t>
+          <t>663212878.2008342</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1449667896.7</v>
+        <v>1907718783.21</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>751.0</t>
+          <t>800.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>816.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>763.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12447.108</t>
+          <t>16158.888</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>54.83</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5263,32 +5263,32 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>57.62</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>674.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>591.4</t>
+          <t>601.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>599.7</t>
+          <t>603.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>612.08</t>
+          <t>614.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>536.26</t>
+          <t>270.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-97.01</t>
+          <t>-90.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935698093.450796</t>
+          <t>4929548641.36344</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8659300159.0</t>
+          <t>12410986088.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4557743140.6</t>
+          <t>6888940927.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2943700170.0</t>
+          <t>4033826236.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1771180630.7</t>
+          <t>1975526023.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1614042970</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>252806564.6700073</t>
+          <t>436939077.2900687</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>940586145.2</v>
+        <v>1449667896.7</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-23.80928100874268</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>7.31764784445801</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>28.02509919012324</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>52.97</t>
+          <t>54.15</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>751.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>651.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,143 +878,143 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>799.533</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,273 +1024,4583 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>8.47</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-3.86</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10.66</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>735.4</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>701.1</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>633.54</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>634.25</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-10.78</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>35.05</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>39.28</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-51.36</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>627878031.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1516353585.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2106062606.14</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-888475554</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-74948604.10702263</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-649518023.26</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>25.49</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>740.0</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>740.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>706.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>617.266</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-75.86</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-5.99</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>8.47</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>10.09</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>745.6</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>695.2</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>631.48</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>633.66</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>39.85</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>40.34</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-50.05</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>696124492.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2883970531.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2126707687.18</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>29518563.01117429</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-630160054.09</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>737.0</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>739.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1116.653</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>722.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-80.90</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-8.03</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-3.99</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>752.0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>688.05</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>628.72</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>632.04</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>42.23</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>40.46</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-49.89</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>779349653.2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4079717323.9</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2168937186.34</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>149460129.7576182</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-567096178.3200001</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-6.48</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>26.03</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>725.0</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>722.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>722.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1008.586</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>745.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-5.37</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-82.40</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-5.10</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-2.14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>49.94</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-0.67</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>756.8</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>681.7</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>626.7</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>630.91</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>15.69</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>46.30</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>40.02</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-50.44</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>855936440.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>4864530439.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2227082877.5</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>279743094.8631054</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-495071225.14</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-3.50</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>769.0</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>769.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>737.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>745.0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>711.087</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-81.30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>70.42</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>80.35</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>760.8</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>624.74</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>629.5</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>26.07</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>48.47</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>38.45</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-52.39</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1032473983.6</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>5522062366.6</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2292721646.52</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>420618425.772247</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-368722471.3</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>27.58</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>759.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1193.09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>758.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-7.21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-57.71</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-3.44</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>79.41</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>82.88</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>15.48</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>764.8</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>662.3</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>621.8</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>627.64</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>48.50</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>35.94</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-55.49</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>915187042.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2404829140.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5686609711.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>2312774767.92</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>564134952.5119295</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-152149242.69</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>27.33</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>775.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>780.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>758.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>758.0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1144.535</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-8.91</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-15.19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>91.21</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>86.14</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>17.70</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>767.6</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>652.15</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>619.2</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>625.75</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>32.80</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-59.38</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>869643968.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>5071816570.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5980378748.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>2324099002.48</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-908562178</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>694368442.54881</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>122848998.31</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>27.76</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-2.52</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1587.408</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>746.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-5.52</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>23.64</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-4.97</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5.66</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-3.35</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>78.02</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>20.18</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>770.8</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>641.35</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>624.02</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>61.71</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>46.68</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>28.87</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-64.25</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1194102943.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>7380084994.6</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5968914067.6</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>2329253341.64</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1411170927</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>798281068.7748979</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>516195779.15</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>26.89</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>755.0</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>774.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>746.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2119.821</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-8.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>89.18</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>93.92</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>20.88</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>764.6</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>632.55</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>613.28</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>622.34</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>46.06</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-69.77</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>1639958136.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>8873124437.8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>5944629753.8</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>2333052998.56</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>849569303.2528446</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>1024920726.63</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>27.58</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9688.689</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-11.03</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>70.54</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6.37</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>34.55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>97.52</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>5.85</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>741.6</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>623.0</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>609.92</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>620.01</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>124.51</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>42.66</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-76.47</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>7405253613.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>10011650749.6</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>5870589709.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>2337679186.88</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>817687226.2755579</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>1667296140.69</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>28.30</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>748.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>788.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>742.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>27.74</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>18118.77</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-9.19</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>69.40</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>64.61</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-4.52</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>93.07</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>97.69</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>15.20</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>705.4</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>612.35</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>606.42</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>617.41</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>172.56</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>35.67</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>13.09</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-83.79</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>4923677621.822511</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>14250124193.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>8968390282.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>5294074253.1</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>2221550552.1</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>663212878.2008342</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>1907718783.21</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>27.83</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>51.87</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>40.07</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>223327</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>電機機械右下上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>816.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>763.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-649518023.26</v>
+        <v>-626216745.24</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,74 +1324,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-630160054.09</v>
+        <v>-649518023.26</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,98 +4436,98 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,74 +4772,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-11.03</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.09</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18118.77</t>
+          <t>9688.689</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>93.07</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.20</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>705.4</t>
+          <t>741.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>612.35</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>606.42</t>
+          <t>609.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>617.41</t>
+          <t>620.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>172.56</t>
+          <t>124.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.79</t>
+          <t>-76.47</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4923677621.822511</t>
+          <t>4918417582.333573</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14250124193.0</t>
+          <t>7405253613.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8968390282.0</t>
+          <t>10011650749.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5294074253.1</t>
+          <t>5870589709.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2221550552.1</t>
+          <t>2337679186.88</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,15 +5439,15 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>663212878.2008342</t>
+          <t>817687226.2755579</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1907718783.21</v>
+        <v>1667296140.69</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>763.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-626216745.24</v>
+        <v>-225925652.2</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-649518023.26</v>
+        <v>-626216745.24</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,74 +1755,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-4.37</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-630160054.09</v>
+        <v>-649518023.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-567096178.3200001</v>
+        <v>-630160054.09</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-495071225.14</v>
+        <v>-567096178.3200001</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-368722471.3</v>
+        <v>-495071225.14</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-152149242.69</v>
+        <v>-368722471.3</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>122848998.31</v>
+        <v>-152149242.69</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>516195779.15</v>
+        <v>122848998.31</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,98 +4867,98 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
+          <t>798281068.7748979</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1024920726.63</v>
+        <v>516195779.15</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9688.689</t>
+          <t>2119.821</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5203,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-4.37</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>49.26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-4.67</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>93.92</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>741.6</t>
+          <t>764.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>623.0</t>
+          <t>632.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>609.92</t>
+          <t>613.28</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>620.01</t>
+          <t>622.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>124.51</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.47</t>
+          <t>-69.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4918417582.333573</t>
+          <t>4923771953.88777</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7405253613.0</t>
+          <t>1639958136.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>10011650749.6</t>
+          <t>8873124437.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5870589709.3</t>
+          <t>5944629753.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2337679186.88</t>
+          <t>2333052998.56</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>817687226.2755579</t>
+          <t>849569303.2528446</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1667296140.69</v>
+        <v>1024920726.63</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>54.22</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>233435</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-225925652.2</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+          <t>-92608315.67016768</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>332708021.9386873</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>9396894111</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-4.27</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-10.88</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>26.64</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>789.0</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>688.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-626216745.24</v>
-      </c>
-      <c r="BD3" t="inlineStr">
+          <t>-169938558.8717777</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-225925652.1964645</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>5759803875</v>
+      </c>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-2.85</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-4.27</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>716.0</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>739.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-649518023.26</v>
-      </c>
-      <c r="BD4" t="inlineStr">
+          <t>-159759087.3581983</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-626216745.2396646</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>848806811</v>
+      </c>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-8.42</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-2.85</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>740.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2206,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2.06</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-4.37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -2266,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-630160054.09</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
+          <t>-74948604.10702263</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-649518023.2571056</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>573954733</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-4.40</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>26.60</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>737.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2697,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2848,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,168 +2878,173 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-567096178.3200001</v>
-      </c>
-      <c r="BD6" t="inlineStr">
+          <t>29518563.01117429</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-630160054.0942674</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>453518166</v>
+      </c>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-6.48</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>725.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3128,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,168 +3314,173 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-495071225.14</v>
-      </c>
-      <c r="BD7" t="inlineStr">
+          <t>149460129.7576182</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-567096178.3225608</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>811169006</v>
+      </c>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-3.50</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-6.48</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>769.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>722.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3559,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3715,168 +3750,173 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-368722471.3</v>
-      </c>
-      <c r="BD8" t="inlineStr">
+          <t>279743094.8631054</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-495071225.1371737</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>757270421</v>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-3.50</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>745.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-11.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3990,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4146,168 +4186,173 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-152149242.69</v>
-      </c>
-      <c r="BD9" t="inlineStr">
+          <t>420618425.772247</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-368722471.2960072</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>543477829</v>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>765.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4421,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>122848998.31</v>
-      </c>
-      <c r="BD10" t="inlineStr">
+          <t>564134952.5119295</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-152149242.6909127</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>915187042</v>
+      </c>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>758.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>516195779.15</v>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>694368442.54881</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>122848998.3053265</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>869643968</v>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.37</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>755.0</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>770.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2119.821</t>
+          <t>1587.408</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-8.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,98 +5353,98 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>78.02</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>20.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>764.6</t>
+          <t>770.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>632.55</t>
+          <t>641.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>613.28</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>622.34</t>
+          <t>624.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>61.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>28.87</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.77</t>
+          <t>-64.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4923771953.88777</t>
+          <t>4936949495.859914</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1639958136.0</t>
+          <t>1194102943.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8873124437.8</t>
+          <t>7380084994.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5944629753.8</t>
+          <t>5968914067.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2333052998.56</t>
+          <t>2329253341.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1411170927</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>849569303.2528446</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>1024920726.63</v>
-      </c>
-      <c r="BD12" t="inlineStr">
+          <t>798281068.7748979</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>516195779.1461916</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1194102943</v>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>50.48</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>233435</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>217325</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>746.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,74 +2642,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-7.27</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,17 +2758,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.19</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>122848998.3053265</t>
+          <t>-152149242.6909127</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>869643968</v>
+        <v>915187042</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1587.408</t>
+          <t>1144.535</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>-15.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>20.18</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>770.8</t>
+          <t>767.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>641.35</t>
+          <t>652.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>624.02</t>
+          <t>625.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>61.71</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-64.25</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936949495.859914</t>
+          <t>4936987441.390244</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1194102943.0</t>
+          <t>869643968.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7380084994.6</t>
+          <t>5071816570.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5968914067.6</t>
+          <t>5980378748.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2329253341.64</t>
+          <t>2324099002.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1411170927</t>
+          <t>-908562178</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>798281068.7748979</t>
+          <t>694368442.54881</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>516195779.1461916</t>
+          <t>122848998.3053265</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1194102943</v>
+        <v>869643968</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.48</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>217325</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>726.45</t>
+          <t>729.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>641.18</t>
+          <t>642.32</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3977678243.4</t>
+          <t>4446393537.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2356977274.04</t>
+          <t>2394527724.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3308931687</v>
+        <v>2917531202</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,112 +3078,112 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.82</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-4.53</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-5.99</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,50 +3284,50 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1144.535</t>
+          <t>1193.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-11.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-57.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>82.88</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>767.6</t>
+          <t>764.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>652.15</t>
+          <t>662.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>619.2</t>
+          <t>621.8</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>625.75</t>
+          <t>627.64</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-55.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936987441.390244</t>
+          <t>4936184159.673353</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>869643968.0</t>
+          <t>915187042.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5071816570.6</t>
+          <t>2404829140.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5980378748.8</t>
+          <t>5686609711.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2324099002.48</t>
+          <t>2312774767.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-908562178</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>694368442.54881</t>
+          <t>564134952.5119295</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>122848998.3053265</t>
+          <t>-152149242.6909127</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>869643968</v>
+        <v>915187042</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>215114</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>758.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>729.6</t>
+          <t>734.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>642.32</t>
+          <t>644.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4446393537.2</t>
+          <t>4705713538.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2394527724.36</t>
+          <t>2381458909.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2917531202</v>
+        <v>2145406818</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>726.45</t>
+          <t>729.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>641.18</t>
+          <t>642.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3977678243.4</t>
+          <t>4446393537.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2356977274.04</t>
+          <t>2394527724.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3308931687</v>
+        <v>2917531202</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>720.75</t>
+          <t>726.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>639.48</t>
+          <t>641.18</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3406595539.2</t>
+          <t>3977678243.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2319670873.56</t>
+          <t>2356977274.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>9396894111</v>
+        <v>3308931687</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>715.55</t>
+          <t>720.75</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>638.3</t>
+          <t>639.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1689450518.2</t>
+          <t>3406595539.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2149905312.46</t>
+          <t>2319670873.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5759803875</v>
+        <v>9396894111</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>708.6</t>
+          <t>715.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>635.96</t>
+          <t>638.3</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>688943827.4</t>
+          <t>1689450518.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2069337538.82</t>
+          <t>2149905312.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>848806811</v>
+        <v>5759803875</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-7.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>701.1</t>
+          <t>708.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>633.54</t>
+          <t>635.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>627878031.0</t>
+          <t>688943827.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2106062606.14</t>
+          <t>2069337538.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>573954733</v>
+        <v>848806811</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,72 +3514,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-4.01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-8.37</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>701.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>633.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>627878031.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>2106062606.14</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>453518166</v>
+        <v>573954733</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>688.05</t>
+          <t>695.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>628.72</t>
+          <t>631.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>779349653.2</t>
+          <t>696124492.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2168937186.34</t>
+          <t>2126707687.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>811169006</v>
+        <v>453518166</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>681.7</t>
+          <t>688.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>626.7</t>
+          <t>628.72</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>855936440.6</t>
+          <t>779349653.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2227082877.5</t>
+          <t>2168937186.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>757270421</v>
+        <v>811169006</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>681.7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>624.74</t>
+          <t>626.7</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1032473983.6</t>
+          <t>855936440.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2292721646.52</t>
+          <t>2227082877.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>543477829</v>
+        <v>757270421</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1193.09</t>
+          <t>711.087</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.31</t>
+          <t>-10.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-57.71</t>
+          <t>-81.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>82.88</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>764.8</t>
+          <t>760.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>662.3</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>621.8</t>
+          <t>624.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>627.64</t>
+          <t>629.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.50</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-55.49</t>
+          <t>-52.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,27 +5464,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4936184159.673353</t>
+          <t>4933726257.051502</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>915187042.0</t>
+          <t>543477829.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2404829140.4</t>
+          <t>1032473983.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5686609711.2</t>
+          <t>5522062366.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2312774767.92</t>
+          <t>2292721646.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>564134952.5119295</t>
+          <t>420618425.772247</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-152149242.6909127</t>
+          <t>-368722471.2960072</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>915187042</v>
+        <v>543477829</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>215114</t>
+          <t>219537</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>759.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>758.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>701.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>734.15</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>644.12</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>734.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>644.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2145406818.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4705713538.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4705713538.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2697328683.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2381458909.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2381458909.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>47833880.16900253</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2145406818</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2145406818.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>712.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>729.6</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>642.32</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>729.6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>642.3200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2917531202.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4446393537.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4446393537.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2537135784.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2394527724.36</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2394527724.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>171300840.0050039</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2917531202</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2917531202.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>726.45</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>641.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>641.1799999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3308931687.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3977678243.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3977678243.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2336901368.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2356977274.04</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2356977274.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>258836711.484827</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3308931687</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3308931687.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>724.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>720.75</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>639.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>720.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>639.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>9396894111.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3406595539.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3406595539.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2092972596.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2319670873.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2319670873.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>332708021.9386873</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>9396894111</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>9396894111.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>731.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>715.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>638.3</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>638.3</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>5759803875.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1689450518.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1689450518.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1272693479.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2149905312.46</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2149905312.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-225925652.1964645</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5759803875</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5759803875.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>732.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>708.6</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>635.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>635.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>848806811.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>688943827.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>688943827.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>860708905.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2069337538.82</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2069337538.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-626216745.2396646</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>848806811</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>848806811.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>735.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>701.1</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>633.54</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>701.1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>633.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>573954733.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>627878031.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>627878031</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1516353585.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2106062606.14</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2106062606.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-649518023.2571056</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>573954733</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>745.6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>695.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>631.48</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>631.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>453518166.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>696124492.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>696124492.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2883970531.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2126707687.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2126707687.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-630160054.0942674</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>453518166</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>752.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>688.05</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>628.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>811169006.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>779349653.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4079717323.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2168937186.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-567096178.3225608</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>811169006</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>756.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>626.7</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>757270421.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>855936440.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4864530439.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2227082877.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-495071225.1371737</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>757270421</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>760.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>673</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>624.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>543477829.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1032473983.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5522062366.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2292721646.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-368722471.2960072</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>543477829</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN6" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.91</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,74 +3908,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6.19</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-4.01</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>624.0</t>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>681.7</v>
+        <v>688.05</v>
       </c>
       <c r="AN11" t="n">
-        <v>626.7</v>
+        <v>628.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>855936440.6</v>
+        <v>779349653.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2227082877.5</v>
+        <v>2168937186.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>711.087</t>
+          <t>1008.586</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.07</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-81.30</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>760.8</t>
+          <t>756.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>673</v>
+        <v>681.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>624.74</v>
+        <v>626.7</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>629.5</t>
+          <t>630.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>46.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>40.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-50.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4933726257.051502</t>
+          <t>4935523146.353572</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1032473983.6</v>
+        <v>855936440.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5522062366.6</t>
+          <t>4864530439.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2292721646.52</v>
+        <v>2227082877.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>420618425.772247</t>
+          <t>279743094.8631054</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-368722471.2960072</t>
+          <t>-495071225.1371737</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>543477829.0</t>
+          <t>757270421.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>53.49</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>219537</t>
+          <t>230277</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,72 +4338,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,102 +4778,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-5.43</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-75.86</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>624.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-5.99</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>0.96</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-80.90</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-8.03</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1008.586</t>
+          <t>1116.653</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-80.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>756.8</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>681.7</v>
+        <v>688.05</v>
       </c>
       <c r="AN12" t="n">
-        <v>626.7</v>
+        <v>628.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>630.91</t>
+          <t>632.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.02</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-49.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935523146.353572</t>
+          <t>4935251699.197575</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>855936440.6</v>
+        <v>779349653.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4864530439.2</t>
+          <t>4079717323.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2227082877.5</v>
+        <v>2168937186.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>279743094.8631054</t>
+          <t>149460129.7576182</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-495071225.1371737</t>
+          <t>-567096178.3225608</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>757270421.0</t>
+          <t>811169006.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>230277</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>722.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,72 +4768,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-5.43</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-4.65</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1116.653</t>
+          <t>617.266</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-80.90</t>
+          <t>-75.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>745.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>688.05</v>
+        <v>695.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>628.72</v>
+        <v>631.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>632.04</t>
+          <t>633.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4935251699.197575</t>
+          <t>4933619914.912393</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>779349653.2</v>
+        <v>696124492.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4079717323.9</t>
+          <t>2883970531.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2168937186.34</v>
+        <v>2126707687.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>149460129.7576182</t>
+          <t>29518563.01117429</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-567096178.3225608</t>
+          <t>-630160054.0942674</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>811169006.0</t>
+          <t>453518166.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>51.87</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>223327</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>722.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN6" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>799.533</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.32</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.62</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-58.59</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-75.86</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>735.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>695.2</v>
+        <v>701.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>631.48</v>
+        <v>633.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>634.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-51.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4933619914.912393</t>
+          <t>4931859360.209104</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>696124492.8</v>
+        <v>627878031</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>1516353585.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2126707687.18</v>
+        <v>2106062606.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-888475554</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>-74948604.10702263</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-630160054.0942674</t>
+          <t>-649518023.2571056</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>573954733.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223327</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【c】</t>
+          <t>價_量;【c】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.54</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>799.533</t>
+          <t>1152.161</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-58.59</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>735.4</t>
+          <t>732.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>701.1</v>
+        <v>708.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>633.54</v>
+        <v>635.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>634.25</t>
+          <t>635.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.36</t>
+          <t>-52.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4931859360.209104</t>
+          <t>4927555242.950284</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>627878031</v>
+        <v>688943827.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1516353585.7</t>
+          <t>860708905.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2106062606.14</v>
+        <v>2069337538.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-888475554</t>
+          <t>-171765078</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-74948604.10702263</t>
+          <t>-159759087.3581983</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-649518023.2571056</t>
+          <t>-626216745.2396646</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>573954733.0</t>
+          <t>848806811.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>223011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【c】;【x】看好</t>
+          <t>【c】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN11" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-24.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1152.161</t>
+          <t>7500.722</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>732.4</t>
+          <t>731.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>708.6</v>
+        <v>715.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>635.96</v>
+        <v>638.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>635.39</t>
+          <t>636.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-54.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4927555242.950284</t>
+          <t>4924195625.746809</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>688943827.4</v>
+        <v>1689450518.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>860708905.5</t>
+          <t>1272693479.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2069337538.82</v>
+        <v>2149905312.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-171765078</t>
+          <t>416757038</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-159759087.3581983</t>
+          <t>-169938558.8717777</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-626216745.2396646</t>
+          <t>-225925652.1964645</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>848806811.0</t>
+          <t>5759803875.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>224591</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>803.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,176 +1014,168 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>9.23</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>706.2</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>721.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>660.24</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>642.91</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-39.98</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-83.87</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/16</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4919856794.394476</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1840994094</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2486803181.6</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2593471789.5</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-645809087</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-87575595.74692756</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-295436683.9736991</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-7.25</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>703.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>722.7</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>657.66</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>642.4</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-45.49</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>7.81</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>14.33</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-82.26</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4924195625.746809</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1706016743.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2225561827.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>3302427213.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2578743388.1</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-1076865386</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-49782670.61478729</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-230075552.3796711</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>1706016743.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-7.90</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1335,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.67</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-2.59</t>
-        </is>
+          <t>43.94</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-2.73</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-48.64</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>8.19</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>15.96</t>
-        </is>
+          <t>-45.49</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.33</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
+          <t>35.67</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-49.29</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>17.90</t>
-        </is>
+          <t>-48.64</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.96</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
+          <t>27.49</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-3.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-42.31</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>11.60</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>20.10</t>
-        </is>
+          <t>-49.29</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.9</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.13</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-4.77</t>
-        </is>
+          <t>44.93</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-4.23</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-41.44</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>22.23</t>
-        </is>
+          <t>-42.31</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20.1</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-5.19</t>
-        </is>
+          <t>39.13</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-4.77</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-37.42</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
+          <t>-41.44</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>22.23</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>14.56</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
+          <t>29.95</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-5.19</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.51</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>26.82</t>
-        </is>
+          <t>-37.42</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>24.53</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.79</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
+          <t>14.56</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.41</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-38.99</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>29.74</t>
-        </is>
+          <t>-43.51</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>26.82</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4212,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-2.3</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.15</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>23.12</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+          <t>-38.99</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>29.74</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.68</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-5.02</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+          <t>24.72</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.16</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-24.05</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
+          <t>-29.15</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>32.64</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7500.722</t>
+          <t>12908.308</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>62.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>46.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5252,48 @@
           <t>39.68</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.51</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>731.2</t>
+          <t>724.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>715.55</v>
+        <v>720.75</v>
       </c>
       <c r="AN12" t="n">
-        <v>638.3</v>
+        <v>639.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>636.88</t>
+          <t>637.48</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.52</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>37.13</t>
-        </is>
+          <t>-24.05</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>35.02</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-54.03</t>
+          <t>-56.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4924195625.746809</t>
+          <t>4919856794.394476</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1689450518.2</v>
+        <v>3406595539.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1272693479.4</t>
+          <t>2092972596.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2149905312.46</v>
+        <v>2319670873.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>416757038</t>
+          <t>1313622943</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-169938558.8717777</t>
+          <t>-92608315.67016768</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-225925652.1964645</t>
+          <t>332708021.9386873</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5759803875.0</t>
+          <t>9396894111.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-10.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>24.80</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>52.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>224591</t>
+          <t>226170</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>803.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>688.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AH3" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AR6" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>4.17</v>
+        <v>-0.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.19</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>15.35</v>
+        <v>13.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>24.53</v>
+        <v>22.23</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.97</v>
+        <v>4.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.41</v>
+        <v>-5.19</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>15.15</v>
+        <v>15.35</v>
       </c>
       <c r="AR9" t="n">
-        <v>26.82</v>
+        <v>24.53</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-4.46</v>
+        <v>-0.97</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.3</v>
+        <v>-4.41</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>18.15</v>
+        <v>15.15</v>
       </c>
       <c r="AR10" t="n">
-        <v>29.74</v>
+        <v>26.82</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.67</v>
+        <v>-4.46</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>23.12</v>
+        <v>18.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>32.64</v>
+        <v>29.74</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-5.02</v>
+        <v>-1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.51</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>26.6</v>
+        <v>23.12</v>
       </c>
       <c r="AR12" t="n">
-        <v>35.02</v>
+        <v>32.64</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3187.546</t>
+          <t>2665.643</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.85</t>
+          <t>-26.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.19</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.48</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>707.8</t>
+          <t>715.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>718.45</v>
+        <v>717.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>662.8200000000001</v>
+        <v>665.6799999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>643.56</t>
+          <t>644.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-35.95</t>
+          <t>-23.49</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>7.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-85.20</t>
+          <t>-86.02</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1791250542.6</v>
+        <v>1684494637.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2383687512.6</t>
+          <t>2284953103.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2625926244.44</v>
+        <v>2600226983.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-592436970</t>
+          <t>-600458466</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-113490037.7497351</t>
+          <t>-134198650.8074806</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-256019468.7651763</t>
+          <t>-248096022.6250811</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AH4" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>4.17</v>
+        <v>-0.31</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.19</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>15.35</v>
+        <v>13.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.53</v>
+        <v>22.23</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.97</v>
+        <v>4.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.41</v>
+        <v>-5.19</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>15.15</v>
+        <v>15.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>26.82</v>
+        <v>24.53</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-4.46</v>
+        <v>-0.97</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.3</v>
+        <v>-4.41</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>18.15</v>
+        <v>15.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>29.74</v>
+        <v>26.82</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.67</v>
+        <v>-4.46</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>23.12</v>
+        <v>18.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>32.64</v>
+        <v>29.74</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4917730635.55587</t>
+          <t>4914874067.809322</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>225854</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】;【x】看好</t>
+          <t>價_量;【b1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2665.643</t>
+          <t>9997.961</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,93 +933,93 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.69</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.01</v>
+        <v>6.68</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>715.6</t>
+          <t>730.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>717.05</v>
+        <v>717.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>665.6799999999999</v>
+        <v>669.5599999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>644.55</t>
+          <t>646.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>8.640000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.29</v>
+        <v>11.67</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,58 +1082,58 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.02</t>
+          <t>-85.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1684494637.6</v>
+        <v>2968183672.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2284953103.8</t>
+          <t>2839040993.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2600226983.84</v>
+        <v>2727391369.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-600458466</t>
+          <t>129142678</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-134198650.8074806</t>
+          <t>-83497291.42731231</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-248096022.6250811</t>
+          <t>195360185.1636133</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>784.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3187.546</t>
+          <t>2665.643</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.85</t>
+          <t>-26.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1355,49 +1355,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,27 +1405,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.19</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.48</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>707.8</t>
+          <t>715.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>718.45</v>
+        <v>717.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>662.8200000000001</v>
+        <v>665.6799999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>643.56</t>
+          <t>644.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.95</t>
+          <t>-23.49</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.20</t>
+          <t>-86.02</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1791250542.6</v>
+        <v>1684494637.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2383687512.6</t>
+          <t>2284953103.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2625926244.44</v>
+        <v>2600226983.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-592436970</t>
+          <t>-600458466</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-113490037.7497351</t>
+          <t>-134198650.8074806</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-256019468.7651763</t>
+          <t>-248096022.6250811</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1777,49 +1777,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AN4" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2199,49 +2199,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AH5" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2621,49 +2621,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2671,27 +2671,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,53 +2770,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3043,49 +3043,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3465,49 +3465,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3515,27 +3515,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3887,49 +3887,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3937,27 +3937,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4309,49 +4309,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4359,27 +4359,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>4.17</v>
+        <v>-0.31</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.19</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>15.35</v>
+        <v>13.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>24.53</v>
+        <v>22.23</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,53 +4458,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4731,49 +4731,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4781,27 +4781,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.97</v>
+        <v>4.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.41</v>
+        <v>-5.19</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>15.15</v>
+        <v>15.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>26.82</v>
+        <v>24.53</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,53 +4880,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5153,49 +5153,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-11-05 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5203,27 +5203,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.46</v>
+        <v>-0.97</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.3</v>
+        <v>-4.41</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>18.15</v>
+        <v>15.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>29.74</v>
+        <v>26.82</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4914874067.809322</t>
+          <t>4924203481.775035</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9997.961</t>
+          <t>7261.441</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>761.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>785.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>93.18</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6.68</v>
+        <v>2.81</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>730.2</t>
+          <t>740.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>717.75</v>
+        <v>718.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>669.5599999999999</v>
+        <v>673.4400000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>646.46</t>
+          <t>648.22</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>13.22</v>
+        <v>15.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.67</v>
+        <v>12.38</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-85.54</t>
+          <t>-84.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7686285713.0</t>
+          <t>5604193383.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2968183672.2</v>
+        <v>3747819000.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2839040993.3</t>
+          <t>2986690413.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2727391369.42</v>
+        <v>2811890417.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>129142678</t>
+          <t>761128586</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-83497291.42731231</t>
+          <t>-17614846.40209365</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>195360185.1636133</t>
+          <t>344738601.236609</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7686285713.0</t>
+          <t>5604193383.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>784.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2665.643</t>
+          <t>9997.961</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,33 +1415,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.69</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.01</v>
+        <v>6.68</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>715.6</t>
+          <t>730.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>717.05</v>
+        <v>717.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>665.6799999999999</v>
+        <v>669.5599999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>644.55</t>
+          <t>646.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>8.640000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.29</v>
+        <v>11.67</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-86.02</t>
+          <t>-85.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1684494637.6</v>
+        <v>2968183672.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2284953103.8</t>
+          <t>2839040993.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2600226983.84</v>
+        <v>2727391369.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-600458466</t>
+          <t>129142678</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-134198650.8074806</t>
+          <t>-83497291.42731231</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-248096022.6250811</t>
+          <t>195360185.1636133</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>784.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3187.546</t>
+          <t>2665.643</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.85</t>
+          <t>-26.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.19</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.48</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>707.8</t>
+          <t>715.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>718.45</v>
+        <v>717.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>662.8200000000001</v>
+        <v>665.6799999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>643.56</t>
+          <t>644.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-35.95</t>
+          <t>-23.49</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>7.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.20</t>
+          <t>-86.02</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1791250542.6</v>
+        <v>1684494637.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2383687512.6</t>
+          <t>2284953103.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2625926244.44</v>
+        <v>2600226983.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-592436970</t>
+          <t>-600458466</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-113490037.7497351</t>
+          <t>-134198650.8074806</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-256019468.7651763</t>
+          <t>-248096022.6250811</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AH6" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4.17</v>
+        <v>-0.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.19</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN11" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>15.35</v>
+        <v>13.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>24.53</v>
+        <v>22.23</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.97</v>
+        <v>4.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.41</v>
+        <v>-5.19</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>15.15</v>
+        <v>15.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>26.82</v>
+        <v>24.53</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4924203481.775035</t>
+          <t>4929107829.088733</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>55.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>246071</t>
+          <t>240385</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ12"/>
+  <dimension ref="A1:CR12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,320 +551,360 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>MA_last_cross_d2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MA_last_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -883,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7261.441</t>
+          <t>11957.03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>807.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +978,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +1018,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,300 +1033,340 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>42.64</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>79.55</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>93.18</t>
         </is>
       </c>
-      <c r="AH2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>3.89</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>740.2</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>718.55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>673.4400000000001</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>648.22</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>22.90</t>
-        </is>
+      <c r="AP2" t="n">
+        <v>6.41</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12.38</v>
+        <v>4.93</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>6.61</t>
+        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>758.4</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>722.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>677.96</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>650.69</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>45.27</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-84.67</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-82.71</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>5604193383.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>3747819000.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>2986690413.7</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2811890417.72</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>761128586</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-17614846.40209365</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>344738601.236609</t>
-        </is>
-      </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5604193383.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+          <t>9487332245.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>5397154690.4</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>3619074392.2</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>2989148428.74</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>1778080298</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>97698274.90696546</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>731920442.1067905</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>9487332245.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>29.09</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>786.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>789.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>755.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>761.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>767.0</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>808.0</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>767.0</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>807.0</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1305,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9997.961</t>
+          <t>7261.441</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,74 +1400,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>761.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.37</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.22</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>785.0</t>
@@ -1400,7 +1480,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,300 +1495,340 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>25.89</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-2.88</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>87.72</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>730.2</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>717.75</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>669.5599999999999</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>79.55</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>646.46</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
+          <t>93.18</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.81</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>11.67</v>
+        <v>3.01</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>740.2</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>718.55</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>673.4400000000001</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>648.22</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>22.90</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-85.54</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-84.67</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>7686285713.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>2968183672.2</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>2839040993.3</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2727391369.42</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>129142678</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-83497291.42731231</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>195360185.1636133</t>
-        </is>
-      </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7686285713.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
+          <t>5604193383.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>3747819000.2</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2986690413.7</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>2811890417.72</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>761128586</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-17614846.40209365</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>344738601.236609</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5604193383.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>28.08</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>27.43</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>745.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>735.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>786.0</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>789.0</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>755.0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>761.0</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1717,7 +1837,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2665.643</t>
+          <t>9997.961</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,22 +1872,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1782,7 +1902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1807,7 +1927,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1822,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,300 +1957,340 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>2025/04/01</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>35.65</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>78.69</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>715.6</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>717.05</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>665.6799999999999</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>644.55</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-23.49</t>
-        </is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.29</v>
+        <v>1.73</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>730.2</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>717.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>669.5599999999999</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>646.46</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>13.22</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-86.02</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-85.54</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>1930187114.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>1684494637.6</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>2284953103.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2600226983.84</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-600458466</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-134198650.8074806</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-248096022.6250811</t>
-        </is>
-      </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
+          <t>7686285713.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>2968183672.2</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2839040993.3</t>
+        </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>2727391369.42</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>129142678</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-83497291.42731231</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>195360185.1636133</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>7686285713.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-5.44</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>28.08</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>721.0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>730.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>715.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>730.0</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>745.0</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>784.0</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>735.0</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2149,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3187.546</t>
+          <t>2665.643</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,395 +2324,435 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-26.28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>479.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>78.69</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>715.6</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>717.05</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>665.6799999999999</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>644.55</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>-23.49</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-86.02</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4942190656.85021</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>1930187114.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>1684494637.6</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2284953103.8</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>2600226983.84</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-600458466</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-134198650.8074806</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-248096022.6250811</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1930187114.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-5.44</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>17.93840330060069</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>13.37012123856452</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>23.64886415022257</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>華城-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>721.0</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6.04</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-2.22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-24.85</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>63.16</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>66.19</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>8.39</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>707.8</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>718.45</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>662.8200000000001</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>643.56</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-35.95</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-85.20</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2277774997.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>1791250542.6</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>2383687512.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2625926244.44</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-592436970</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-113490037.7497351</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-256019468.7651763</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2277774997.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-7.38</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>25.78</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>730.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>704.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>715.0</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2571,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2826,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,300 +2881,340 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>11.37</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>9.23</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>706.2</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>721.2</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>660.24</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>63.16</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>642.91</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-39.98</t>
-        </is>
+          <t>66.19</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.02</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13.02</v>
+        <v>-1.48</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>8.39</t>
+        </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>707.8</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>718.45</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>662.8200000000001</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>643.56</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>-35.95</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-83.87</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-85.20</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1240653794.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>1840994094</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>2486803181.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2593471789.5</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-645809087</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-87575595.74692756</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-295436683.9736991</t>
-        </is>
-      </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
+          <t>2277774997.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>1791250542.6</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2383687512.6</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>2625926244.44</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-592436970</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-113490037.7497351</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-256019468.7651763</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2277774997.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-7.25</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-7.38</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>25.78</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>716.0</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2993,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,300 +3343,340 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>703.0</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>722.7</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>657.66</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>642.4</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-45.49</t>
-        </is>
+      <c r="AP7" t="n">
+        <v>1.39</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14.33</v>
+        <v>-2.08</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>9.23</t>
+        </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>706.2</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>721.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>660.24</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>642.91</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>-39.98</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-82.26</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-83.87</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>1706016743.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>2225561827.2</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>3302427213.3</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2578743388.1</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-1076865386</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-49782670.61478729</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-230075552.3796711</t>
-        </is>
-      </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>1840994094</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2486803181.6</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>2593471789.5</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-645809087</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-87575595.74692756</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-295436683.9736991</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>1240653794.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-7.90</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-7.25</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>25.63</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>25.81</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>705.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>694.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>711.0</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>708.0</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>716.0</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3415,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,300 +3805,340 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>8.59</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>52.08</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>10.71</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>706.6</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>725.4</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>655.24</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>641.96</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-48.64</t>
-        </is>
+          <t>43.94</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.96</v>
+        <v>-2.73</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>703.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>722.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>657.66</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>642.4</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>-45.49</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-80.24</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-82.26</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>1267840540.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>2709898314.4</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>3707805926.5</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2561747225.36</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-997907612</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-17002146.65753568</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-178345839.1960711</t>
-        </is>
-      </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
+          <t>1706016743.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>2225561827.2</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>3302427213.3</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>2578743388.1</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-1076865386</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-49782670.61478729</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-230075552.3796711</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1706016743.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-8.55</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-7.90</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>25.63</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>703.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>692.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>705.0</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>715.0</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>694.0</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>711.0</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3837,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +4212,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,300 +4267,340 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>11.69</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>704.4</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>729.35</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>653</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>52.08</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>641.5</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-49.29</t>
-        </is>
+          <t>35.67</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17.9</v>
+        <v>-2.59</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>10.71</t>
+        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>706.6</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>725.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>655.24</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>641.96</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>-48.64</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-77.84</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-80.24</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2463966639.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>2885411570</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>3665902553.6</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2552773254.62</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-780490983</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>12333070.16765259</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-51129304.35535431</t>
-        </is>
-      </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
+          <t>1267840540.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>2709898314.4</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>3707805926.5</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>2561747225.36</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-997907612</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-17002146.65753568</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-178345839.1960711</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1267840540.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-10.49</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-8.55</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>24.91</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>711.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>718.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>691.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>691.0</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>703.0</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>706.0</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>692.0</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>706.0</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4259,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,300 +4729,340 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>12.54</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-3.91</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>37.68</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-4.23</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>702.4</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>733.4</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>650.8200000000001</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>17.24</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>641.01</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-42.31</t>
-        </is>
+          <t>27.49</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20.1</v>
+        <v>-3.42</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>11.69</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>704.4</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>729.35</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>653</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>641.5</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>-49.29</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-75.11</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-77.84</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2526492754.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>2976124482.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>3476901363.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2522196255.28</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-500776880</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>23871683.71729021</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>4278281.394074917</t>
-        </is>
-      </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
+          <t>2463966639.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>2885411570</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>3665902553.6</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>2552773254.62</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-780490983</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>12333070.16765259</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-51129304.35535431</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>2463966639.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-8.42</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-10.49</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>24.91</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>717.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>727.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>707.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>707.0</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>711.0</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>718.0</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4681,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +5136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,300 +5191,340 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>12.57</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-2.83</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>27.54</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>39.13</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>702.2</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>737.35</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>648.52</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>37.68</t>
+        </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>640.28</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-41.44</t>
-        </is>
+          <t>44.93</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.65</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.01</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>22.23</v>
+        <v>-4.23</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>12.69</t>
+        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>702.4</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>733.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>650.8200000000001</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>641.01</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-42.31</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-72.48</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-75.11</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>3163492460.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>3132612269.2</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>3269603904.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2494838192.4</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-136991635</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>27434120.50332935</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>76579952.95061398</t>
-        </is>
-      </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+          <t>2526492754.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>2976124482.6</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>3476901363.0</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>2522196255.28</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-500776880</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>23871683.71729021</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>4278281.394074917</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>2526492754.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-9.33</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-8.42</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>25.49</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>698.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>717.0</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>727.0</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>707.0</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5103,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>13.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5598,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,300 +5653,340 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>15.89</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-5.14</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>69.57</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>699.8</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>738.1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>646.54</v>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>27.54</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>639.58</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-37.42</t>
-        </is>
+          <t>39.13</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>24.53</v>
+        <v>-4.77</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>702.2</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>737.35</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>648.52</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>640.28</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>-41.44</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-69.62</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-72.48</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>4929107829.088733</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>4127699179.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>4379292599.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>3034371558.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2446536212.66</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>1344921040</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>18498514.60382305</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>108883088.3545771</t>
-        </is>
-      </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>4942190656.85021</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+          <t>3163492460.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>3132612269.2</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>3269603904.2</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>2494838192.4</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>-136991635</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>27434120.50332935</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>76579952.95061398</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>3163492460.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-5.57</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-9.33</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>26.28</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>25.23</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>41.81</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>240385</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>42.24</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>254915</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>704.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>743.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>704.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>729.0</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>698.0</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11957.03</t>
+          <t>16269.853</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>807.0</t>
+          <t>802.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>62.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,92 +1068,92 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.05</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>93.18</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>6.41</v>
+        <v>3.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.93</v>
+        <v>6.86</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>758.4</t>
+          <t>775.8</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>722.8</v>
+        <v>726</v>
       </c>
       <c r="AV2" t="n">
-        <v>677.96</v>
+        <v>682.48</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>650.69</t>
+          <t>653.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>48.61</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>20.28</v>
+        <v>23.62</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.96</v>
+        <v>15.89</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-82.71</t>
+          <t>-80.32</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,48 +1172,48 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>9487332245.0</t>
+          <t>13512163309.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>5397154690.4</v>
+        <v>7644032352.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>3619074392.2</t>
+          <t>4717641447.7</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>2989148428.74</v>
+        <v>3245403227.06</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1778080298</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>97698274.90696546</t>
+          <t>280592701.7617781</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>731920442.1067905</t>
+          <t>1286512049.463247</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>9487332245.0</t>
+          <t>13512163309.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>28.91</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>818.0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>808.0</t>
+          <t>856.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>800.0</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>807.0</t>
+          <t>802.0</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7261.441</t>
+          <t>11957.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>807.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,17 +1556,17 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1575,47 +1575,47 @@
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>2.81</v>
+        <v>6.41</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.01</v>
+        <v>4.93</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>740.2</t>
+          <t>758.4</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>718.55</v>
+        <v>722.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>673.4400000000001</v>
+        <v>677.96</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>648.22</t>
+          <t>650.69</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>15.22</v>
+        <v>20.28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.38</v>
+        <v>13.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-84.67</t>
+          <t>-82.71</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>5604193383.0</t>
+          <t>9487332245.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>3747819000.2</v>
+        <v>5397154690.4</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2986690413.7</t>
+          <t>3619074392.2</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>2811890417.72</v>
+        <v>2989148428.74</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>761128586</t>
+          <t>1778080298</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-17614846.40209365</t>
+          <t>97698274.90696546</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>344738601.236609</t>
+          <t>731920442.1067905</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>5604193383.0</t>
+          <t>9487332245.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>786.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>789.0</t>
+          <t>808.0</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>761.0</t>
+          <t>807.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9997.961</t>
+          <t>7261.441</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,74 +1862,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>761.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25.48</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>785.0</t>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.55</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>93.18</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>6.68</v>
+        <v>2.81</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>730.2</t>
+          <t>740.2</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>717.75</v>
+        <v>718.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>669.5599999999999</v>
+        <v>673.4400000000001</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>646.46</t>
+          <t>648.22</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>13.22</v>
+        <v>15.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.67</v>
+        <v>12.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-85.54</t>
+          <t>-84.67</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,48 +2096,48 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>7686285713.0</t>
+          <t>5604193383.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>2968183672.2</v>
+        <v>3747819000.2</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2839040993.3</t>
+          <t>2986690413.7</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>2727391369.42</v>
+        <v>2811890417.72</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>129142678</t>
+          <t>761128586</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-83497291.42731231</t>
+          <t>-17614846.40209365</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>195360185.1636133</t>
+          <t>344738601.236609</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7686285713.0</t>
+          <t>5604193383.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>786.0</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>784.0</t>
+          <t>789.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>761.0</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2665.643</t>
+          <t>9997.961</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,22 +2334,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2454,38 +2454,38 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2495,51 +2495,51 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>78.69</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>2.01</v>
+        <v>6.68</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.2</v>
+        <v>1.73</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>715.6</t>
+          <t>730.2</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>717.05</v>
+        <v>717.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>665.6799999999999</v>
+        <v>669.5599999999999</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>644.55</t>
+          <t>646.46</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>8.640000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.29</v>
+        <v>11.67</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-86.02</t>
+          <t>-85.54</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,48 +2558,48 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>1684494637.6</v>
+        <v>2968183672.2</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2284953103.8</t>
+          <t>2839040993.3</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>2600226983.84</v>
+        <v>2727391369.42</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-600458466</t>
+          <t>129142678</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-134198650.8074806</t>
+          <t>-83497291.42731231</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-248096022.6250811</t>
+          <t>195360185.1636133</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1930187114.0</t>
+          <t>7686285713.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>784.0</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3187.546</t>
+          <t>2665.643</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.85</t>
+          <t>-26.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>66.19</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.48</v>
+        <v>-0.2</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>707.8</t>
+          <t>715.6</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>718.45</v>
+        <v>717.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>662.8200000000001</v>
+        <v>665.6799999999999</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>643.56</t>
+          <t>644.55</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-35.95</t>
+          <t>-23.49</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>7.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.95</v>
+        <v>11.29</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-85.20</t>
+          <t>-86.02</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>1791250542.6</v>
+        <v>1684494637.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2383687512.6</t>
+          <t>2284953103.8</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>2625926244.44</v>
+        <v>2600226983.84</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-592436970</t>
+          <t>-600458466</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-113490037.7497351</t>
+          <t>-134198650.8074806</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-256019468.7651763</t>
+          <t>-248096022.6250811</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2277774997.0</t>
+          <t>1930187114.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>730.0</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CM7" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CN7" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AP8" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>11.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,22 +4969,22 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AV11" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>457</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4942190656.85021</t>
+          <t>4963716014.022472</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>254915</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>58.02</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-6.48</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>95.05</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>91.53</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>6.86</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>6.38</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>775.8</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>726</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>682.48</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>653.08</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>48.61</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>23.62</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>15.89</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-80.32</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>13512163309.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>7644032352.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>4717641447.7</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>3245403227.06</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-2147483648</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>280592701.7617781</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>1286512049.463247</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>13512163309.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>3.89</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>28.91</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>818.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>856.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>800.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>802.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>42.64</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>5.09</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>93.18</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>6.41</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>4.93</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>6.61</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>4.19</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>758.4</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>722.8</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>677.96</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>650.69</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>45.27</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>20.28</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>13.96</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-82.71</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>9487332245.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>5397154690.4</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>3619074392.2</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>2989148428.74</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1778080298</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>97698274.90696546</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>731920442.1067905</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>9487332245.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>4.53</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>29.09</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>767.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>808.0</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>767.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>807.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>25.89</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-2.88</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>79.55</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>93.18</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>2.81</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>3.89</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>740.2</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>718.55</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>673.4400000000001</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>648.22</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>22.90</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>15.22</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>12.38</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-84.67</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>5604193383.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>3747819000.2</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>2986690413.7</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>2811890417.72</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>761128586</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-17614846.40209365</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>344738601.236609</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>5604193383.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-1.42</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>27.43</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>786.0</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>789.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>755.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>761.0</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>35.65</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>5.34</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>87.72</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>6.68</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.73</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>730.2</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>717.75</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>669.5599999999999</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>646.46</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>13.22</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>13.22</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>11.67</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-85.54</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>7686285713.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>2968183672.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>2839040993.3</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>2727391369.42</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>129142678</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-83497291.42731231</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>195360185.1636133</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>7686285713.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>28.08</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>745.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>784.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>735.0</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>779.0</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>9.51</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>78.69</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>2.01</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>3.28</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>715.6</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>717.05</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>665.6799999999999</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>644.55</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-23.49</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>11.29</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-86.02</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>1930187114.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>1684494637.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>2284953103.8</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>2600226983.84</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-600458466</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-134198650.8074806</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-248096022.6250811</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>1930187114.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-5.44</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>26.32</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>721.0</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>730.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>730.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>11.37</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-0.54</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>63.16</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>66.19</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>1.02</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-1.48</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>8.39</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>2.99</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>707.8</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>718.45</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>662.8200000000001</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>643.56</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-35.95</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>7.65</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>11.95</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-85.20</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>2277774997.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>1791250542.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>2383687512.6</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>2625926244.44</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-592436970</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-113490037.7497351</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-256019468.7651763</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>2277774997.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-7.38</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>25.78</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>720.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>730.0</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>6.19</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>72.92</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>1.39</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-2.08</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>9.23</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>2.70</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>706.2</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>721.2</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>660.24</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>642.91</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-39.98</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>7.82</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>13.02</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-83.87</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>1240653794.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>1840994094</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>2486803181.6</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>2593471789.5</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-645809087</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-87575595.74692756</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-295436683.9736991</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>1240653794.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-7.25</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>25.81</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>720.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>708.0</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>716.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>8.59</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>43.94</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>1.14</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-2.73</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>9.89</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>703.0</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>722.7</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>657.66</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>642.4</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-45.49</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>7.81</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>14.33</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-82.26</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>1706016743.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>2225561827.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>3302427213.3</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>2578743388.1</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-1076865386</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-49782670.61478729</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-230075552.3796711</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>1706016743.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-7.90</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>25.63</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>705.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>715.0</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>694.0</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>711.0</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>6.47</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>52.08</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>35.67</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-2.59</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>10.71</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>706.6</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>725.4</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>655.24</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>641.96</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-48.64</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>8.19</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>15.96</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-80.24</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>1267840540.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>2709898314.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>3707805926.5</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>2561747225.36</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-997907612</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-17002146.65753568</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-178345839.1960711</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>1267840540.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-8.55</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>703.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>706.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>692.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>706.0</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>12.54</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-3.91</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>17.24</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>27.49</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-1.9</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-3.42</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>11.69</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>704.4</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>729.35</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>653</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>641.5</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-49.29</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>9.08</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>17.9</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-77.84</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>2463966639.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>2885411570</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>3665902553.6</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>2552773254.62</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-780490983</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>12333070.16765259</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-51129304.35535431</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>2463966639.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-10.49</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>24.91</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>711.0</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>718.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/09/08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>629.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/04/01</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>430.0</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>12.57</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.83</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>457</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>16270</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>37.68</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>44.93</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.65</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-4.23</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>12.69</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>702.4</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>733.4</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>650.8200000000001</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>641.01</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-42.31</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>11.6</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>20.1</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>80.75</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-75.11</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/10</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>4963716014.022472</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>2526492754.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>2976124482.6</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>3476901363.0</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>2522196255.28</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-500776880</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>23871683.71729021</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>4278281.394074917</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>2526492754.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>772.0</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/11/04</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-8.42</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>華城</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>17.93840330060069</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>13.37012123856452</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>23.64886415022257</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>25.49</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>58.84</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>41.69%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>20.62%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>253336</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>華城-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>717.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>727.0</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>707.0</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>707.0</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>27.74</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/變壓器.xlsx
+++ b/Result/checksun_type/變壓器.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16269.853</t>
+          <t>10261.373</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>802.0</t>
+          <t>798.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.03</t>
+          <t>68.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>95.05</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>95.22</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>3.38</v>
+        <v>1.09</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.86</v>
+        <v>8.06</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>775.8</t>
+          <t>789.4</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>726</v>
+        <v>730.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>682.48</v>
+        <v>687.1799999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>653.08</t>
+          <t>655.41</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>48.61</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>23.62</v>
+        <v>25.65</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.89</v>
+        <v>17.84</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-80.32</t>
+          <t>-77.90</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>4963716014.022472</t>
+          <t>4974124470.753156</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>13512163309.0</t>
+          <t>8256630442.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7644032352.8</v>
+        <v>8909321018.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>4717641447.7</t>
+          <t>5296907828.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>3245403227.06</v>
+        <v>3388298921.02</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -1238,22 +1238,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>280592701.7617781</t>
+          <t>429485887.3909179</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1286512049.463247</t>
+          <t>1248398408.351187</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>13512163309.0</t>
+          <t>8256630442.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.55</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>253336</t>
+          <t>252072</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>818.0</t>
+          <t>812.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>856.0</t>
+          <t>834.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>802.0</t>
+          <t>798.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11957.03</t>
+          <t>16269.853</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>807.0</t>
+          <t>802.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>62.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,87 +1595,87 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>93.18</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>6.41</v>
+        <v>3.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.93</v>
+        <v>6.86</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>758.4</t>
+          <t>775.8</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>722.8</v>
+        <v>726</v>
       </c>
       <c r="AZ3" t="n">
-        <v>677.96</v>
+        <v>682.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>650.69</t>
+          <t>653.08</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>48.61</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>20.28</v>
+        <v>23.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.96</v>
+        <v>15.89</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-82.71</t>
+          <t>-80.32</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4963716014.022472</t>
+          <t>4974124470.753156</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>9487332245.0</t>
+          <t>13512163309.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>5397154690.4</v>
+        <v>7644032352.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>3619074392.2</t>
+          <t>4717641447.7</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>2989148428.74</v>
+        <v>3245403227.06</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1778080298</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>97698274.90696546</t>
+          <t>280592701.7617781</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>731920442.1067905</t>
+          <t>1286512049.463247</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>9487332245.0</t>
+          <t>13512163309.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>